--- a/Firmware/Modules/Charger/Charger_State_Machine.xlsx
+++ b/Firmware/Modules/Charger/Charger_State_Machine.xlsx
@@ -11,6 +11,7 @@
     <sheet name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="۲ گذارها" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="۳ باتری خراب" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="۴ خطای فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,7 +57,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,13 +147,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,13 +162,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -615,72 +621,89 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>۴ خطای فنی</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ماشین حالت سناریوی ۷ و قفل طبقهٔ قدرت</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>charger.c (EvaluateTechnicalFault/Run)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>فایل‌های مرجع</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Firmware/Modules/Charger/charger.c</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>برگهٔ اعتبارسنجی همین ماژول</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Charger_Validation.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>برگهٔ اعتبارسنجی همین ماژول</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Charger_Validation.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
@@ -691,8 +714,8 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1515,4 +1538,171 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ماشین حالت سناریوی ۷ — تشخیص سوختن ترانزیستور و قفل RAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>حالت</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>شرط ورود</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>خروجی اجباری</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>شرط خروج</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>چهره/پارامتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>عادی</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>لچ فنی خاموش و snapshot معتبر</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>شارژ طبق کنترل عادی</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>امضای فنی اتصال‌کوتاه یا قطع‌شدن</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>اتصال‌کوتاه/سوختن</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>رله باز + PWM واقعی صفر + JIT</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>FAULT_CHARGER_TECHNICAL و FinalDisconnect</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>فقط reset/power-cycle</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>q137..q142</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>قطع‌شدن/سوختن</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>PWM واقعی &gt;۲۰٪ + جریان همان کانال = ۰</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>FAULT_CHARGER_TECHNICAL و FinalDisconnect</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>فقط reset/power-cycle</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>q137..q142</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>قفل نشست برق</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>TechnicalFaultLockout فعال</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>هر دو PWM صفر، رله باز؛ هیچ retry یا پنل/NVM آزاد نمی‌کند</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>func__Charger_Init پس از reset</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>RAM-only</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Charger/Charger_State_Machine.xlsx
+++ b/Firmware/Modules/Charger/Charger_State_Machine.xlsx
@@ -71,7 +71,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,7 +533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -724,7 +724,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -997,7 +997,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1336,7 +1336,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1543,7 +1543,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/Charger/Charger_State_Machine.xlsx
+++ b/Firmware/Modules/Charger/Charger_State_Machine.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ده حالت هر کانال شارژ</t>
+          <t>یازده حالت هر کانال شارژ</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>سه تریپ پیاپی: قفل نهایی کانال</t>
+          <t>سه تریپ همان کانال: قفل نهایی کانال</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -967,20 +967,42 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>CHG_STATE_THERMAL_REST</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>استراحت حرارتی پس از یک ساعت نزدیک سقف جریان</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>صفر (۱۰ دقیقه)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>پایان استراحت ← برگشت به همان فاز شارژ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
           <t>CHG_STATE_MANUAL</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>مود تست دستی؛ duty از پنل می‌آید</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>مقدار فرمان‌شده از پنل</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>خروج از مود یا سکوت ۳ ثانیه‌ای لینک</t>
         </is>

--- a/Firmware/Modules/Charger/Charger_State_Machine.xlsx
+++ b/Firmware/Modules/Charger/Charger_State_Machine.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>معتبرشدن ولتاژ ورودی ← OFF</t>
+          <t>برگشت مجوز مشترک اشمیت Fault (پنجرهٔ ۳۳/۳۴ + حاشیه‌های ۱۶۹/۱۷۰) ← OFF</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1294,54 +1294,76 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>ولتاژ ورودی زیر حد اعتبار</t>
+          <t>خروج ورودی از پنجرهٔ خام مشترک ۳۳/۳۴</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>به‌جز FINAL_FAULT</t>
+          <t>به‌جز FINAL_FAULT؛ توقف فوری</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>INPUT_WAIT</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>مجوز مشترک اشمیت Fault درست است (پنجرهٔ ۳۳/۳۴ + حاشیه‌های برگشت ۱۶۹/۱۷۰)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>شروع نرم دوباره؛ هر شروع OFF-&gt;BULK همان مجوز مشترک را می‌خواهد</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>هر حالت</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>فعال‌شدن مود تست دستی از پنل</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>گیت‌های باتری دور زده می‌شوند</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>خروج از مود یا سکوت ۳ ثانیه‌ای لینک</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>duty صفر و بازگشت به خودکار</t>
         </is>

--- a/Firmware/Modules/Charger/Charger_State_Machine.xlsx
+++ b/Firmware/Modules/Charger/Charger_State_Machine.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ گذارها" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="۳ باتری خراب" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="۴ خطای فنی" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ گذارها" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۳ باتری خراب" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۴ خطای فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
